--- a/backend/data/financials_by_company/1195.HK.xlsx
+++ b/backend/data/financials_by_company/1195.HK.xlsx
@@ -4070,7 +4070,7 @@
         <v>-5249000</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
         <v>0.142</v>
@@ -4258,7 +4258,7 @@
         <v>0.014</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DS2" t="n">
         <v>-0.0033</v>
